--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -4425,7 +4425,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 13.0, "op_wape_pct": 18.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 198.97, "rev_act": 242.19, "op_pred": 33.86, "op_act": 29.53}, {"q": "2025Q4", "rev_pred": 253.45, "rev_act": 258.99, "op_pred": 43.14, "op_act": 24.37}, {"q": "2026Q1", "rev_pred": 227.13, "rev_act": 250.21, "op_pred": 38.66, "op_act": 40.26}, {"q": "2026Q2", "rev_pred": 247.23, "rev_act": 313.58, "op_pred": 42.08, "op_act": 42.97}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 13.0, "op_wape_pct": 18.7, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 198.97, "rev_act": 242.19, "op_pred": 33.86, "op_act": 29.53}, {"q": "2025Q4", "rev_pred": 253.45, "rev_act": 258.99, "op_pred": 43.14, "op_act": 24.37}, {"q": "2026Q1", "rev_pred": 227.13, "rev_act": 250.21, "op_pred": 38.66, "op_act": 40.26}, {"q": "2026Q2", "rev_pred": 247.23, "rev_act": 313.58, "op_pred": 42.08, "op_act": 42.97}]}</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3320</v>
+        <v>3240</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3230</v>
+        <v>3190</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3305</v>
+        <v>3283.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>3320</v>
+        <v>3240</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06081722873705049</v>
+        <v>0.06081722873705048</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.009594524084542878</v>
+        <v>0.009594524084542651</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.05273280727425737</v>
+        <v>0.0527328072742572</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.17</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3240</v>
+        <v>3045</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3190</v>
+        <v>3045</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3283.3</v>
+        <v>3228.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>3240</v>
+        <v>3045</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.91</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3045</v>
+        <v>3065</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3045</v>
+        <v>2990</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3228.8</v>
+        <v>3207</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>3045</v>
+        <v>3065</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,205원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.25</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06081722873705048</v>
+        <v>0.06081722873705049</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.009594524084542651</v>
+        <v>0.009594524084542878</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0527328072742572</v>
+        <v>0.05273280727425737</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3065</v>
+        <v>3015</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3207</v>
+        <v>3197</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>3065</v>
+        <v>3015</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,205원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,070원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06081722873705049</v>
+        <v>0.06081722873705048</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.009594524084542878</v>
+        <v>0.009594524084542651</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.05273280727425737</v>
+        <v>0.0527328072742572</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.32</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3015</v>
+        <v>2850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2990</v>
+        <v>2750</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3197</v>
+        <v>3139.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>3015</v>
+        <v>2850</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.15</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2850</v>
+        <v>2780</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2750</v>
+        <v>2615</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3139.2</v>
+        <v>3084.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2850</v>
+        <v>2780</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,070원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,020원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.59</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2780</v>
+        <v>2825</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3084.3</v>
+        <v>3060</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2780</v>
+        <v>2825</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,020원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,860원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.359999999999999</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2825</v>
+        <v>2770</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2615</v>
+        <v>2500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3060</v>
+        <v>2966.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2825</v>
+        <v>2770</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,860원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,560원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.51</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/073010_model.xlsx
+++ b/argus/kship/models/073010_model.xlsx
@@ -3884,7 +3884,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4755,35 +4755,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4874,35 +4874,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4993,35 +4993,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5112,35 +5112,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5231,35 +5231,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5350,35 +5350,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5469,35 +5469,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5588,35 +5588,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5723,7 +5723,7 @@
         <v>3325</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2770</v>
+        <v>2435</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5905,7 +5905,7 @@
         <v>2050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2500</v>
+        <v>2405</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5996,7 +5996,7 @@
         <v>2917.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2966.4</v>
+        <v>2843.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>2770</v>
+        <v>2435</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,560원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,590원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31893,7 +31893,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33901,7 +33901,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.32</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -33911,7 +33911,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="33">
